--- a/tasks/finalpool/yf-sector-scholarly-excel-word/groundtruth_workspace/Sector_Analysis_Report.xlsx
+++ b/tasks/finalpool/yf-sector-scholarly-excel-word/groundtruth_workspace/Sector_Analysis_Report.xlsx
@@ -455,13 +455,13 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>170</v>
+        <v>202.05</v>
       </c>
       <c r="D2" t="n">
-        <v>170</v>
+        <v>3639745445888</v>
       </c>
       <c r="E2" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="3">
@@ -474,13 +474,13 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>180</v>
+        <v>206.45</v>
       </c>
       <c r="D3" t="n">
-        <v>180</v>
+        <v>2350303674368</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="4">
@@ -493,13 +493,13 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>110</v>
+        <v>111.68</v>
       </c>
       <c r="D4" t="n">
-        <v>110</v>
+        <v>628181237760</v>
       </c>
       <c r="E4" t="n">
-        <v>0.35</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="5">
@@ -512,13 +512,13 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>200</v>
+        <v>249.65</v>
       </c>
       <c r="D5" t="n">
-        <v>200</v>
+        <v>791713873920</v>
       </c>
       <c r="E5" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="6">
@@ -531,10 +531,10 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>155</v>
+        <v>164.11</v>
       </c>
       <c r="D6" t="n">
-        <v>155</v>
+        <v>577484095488</v>
       </c>
       <c r="E6" t="n">
         <v>0.18</v>
@@ -579,17 +579,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sector Rotation Patterns</t>
+          <t>Industry Momentum</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cyclical rotation every 3-5 years</t>
+          <t>Momentum persists 6-12 months</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -601,22 +601,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Industry Momentum</t>
+          <t>Sector Rotation Patterns</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Momentum persists 6-12 months</t>
+          <t>Cyclical rotation every 3-5 years</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>All</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Confirmed</t>
         </is>
       </c>
     </row>
